--- a/나라장터/G2B_Executive_Report.xlsx
+++ b/나라장터/G2B_Executive_Report.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Tracked Bids: 62   |   Total Files Extracted: 85</t>
+          <t>Total Tracked Bids: 71   |   Total Files Extracted: 88</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>R26BK01675718</t>
+          <t>R26BK01687388</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>주식회사 레드브릭스</t>
+          <t>경기도 화성시 효행구보건소</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>‘26년 콘텐츠 제작지원사업 생성형 AI 프로그램 구독권 공급 용역</t>
+          <t>AI 기반 아동청소년 건강관리사업 운영 물품 구입</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -705,37 +705,37 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/</t>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01687388&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>R26BK01679276</t>
+          <t>R26BK01675718</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>연암공과대학교산학협력단</t>
+          <t>주식회사 레드브릭스</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>연암공과대학교 전주기 학생 케어링 AI Counselor 시스템 개발 용역</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
+          <t>‘26년 콘텐츠 제작지원사업 생성형 AI 프로그램 구독권 공급 용역</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -747,30 +747,30 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R26BK01675011</t>
+          <t>R26BK01679276</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026/08/10</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>경기도 의정부시</t>
+          <t>연암공과대학교산학협력단</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>청년AI창업지원센터 조성 인테리어 디자인 및 실시설계</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
+          <t>연암공과대학교 전주기 학생 케어링 AI Counselor 시스템 개발 용역</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -782,100 +782,205 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R26BK01675536</t>
+          <t>R26BK01686876</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>광주과학기술원</t>
+          <t>현대자동차(주)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>서버용 고성능 GPU 보드, 메모리</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
+          <t>AI 특화 공동훈련센터 머신비전 실습교육 시스템 구축</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/</t>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01686876&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>2026MHD005633393</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>방위사업청(운영지원과)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>국방 피지컬AI 자율성 등 활용방안 연구용역</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=2026MHD005633393&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01675011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>경기도 의정부시</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>청년AI창업지원센터 조성 인테리어 디자인 및 실시설계</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01675536</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>광주과학기술원</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>서버용 고성능 GPU 보드, 메모리</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>R26BK01681958</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍I대학성남캠퍼스</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍대학 성남캠퍼스 피지컬 AI센터 구축 공사(건축)</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>소액공사 수의계약 견적서 제출 안내서_피지컬AI센터 구축 공사(전기).hwp
 소액공사 수의계약 견적서 제출 안내서_피지컬AI센터 구축 공사(전기).pdf
 성남캠퍼스 피지컬 AI센터 구축공사 공내역서(전기).xlsx</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01681958&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>R26BK01684842</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>전남광주통합특별시교육청 전남고등학교</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>전남고등학교 AI 융합형 교육실 건축 및 기계설비공사 수의계약 안내 공고</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026학년도 전남고등학교AI 융합형 교육실 건축 및 기계설비공사 수의계약 안내공고문.hwp
 2026학년도 전남고등학교AI 융합형 교육실 건축 및 기계설비공사 수의계약 안내공고문.pdf
@@ -884,37 +989,37 @@
 입찰유의서 및 계약 일반조건.hwp</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01684842&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>R26BK01676734</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>한진부산컨테이너터미널 주식회사</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>AI 기반 ‘충돌·압착 자동 정지’ 및 위험 경보 시스템(STS)</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 입찰공고.pdf
 2. 적격심사기준표_1.pdf
@@ -922,109 +1027,109 @@
 4. AI 기반 ‘충돌·압착 자동 정지’ 및 위험 경보 시스템 시방서.pdf</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01676734&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>R26BK01682417</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>자본재공제조합</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>AI 보증신청 및 챗봇 시스템 개발</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>소액공사 수의계약 견적서 제출 안내서_피지컬AI센터 구축 공사(전기).hwp
 소액공사 수의계약 견적서 제출 안내서_피지컬AI센터 구축 공사(전기).pdf
 성남캠퍼스 피지컬 AI센터 구축공사 공내역서(전기).xlsx</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01682417&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>R26BK01677370</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>주식회사 디에스피</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>지역 주도형 AI대전환 사업 AI 실증 테스트를 위한 Flipper 제작</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>R26BK01685140</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>전남광주통합특별시교육청 전남고등학교</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>전남고등학교 AI 융합형 교육실 전기공사 수의계약 안내 공고</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026학년도 전남고등학교AI 융합형 교육실 전기공사 수의계약 안내공고문.hwp
 2026학년도 전남고등학교AI 융합형 교육실 전기공사 수의계약 안내공고문.pdf
@@ -1033,121 +1138,16 @@
 입찰유의서 및 계약 일반조건.hwp</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685140&amp;bidseq=000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01667120</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>재단법인 경북자동차임베디드연구원</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>재직자 Skill-Up 훈련 교육용 AI 머신 운용관리 용역</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01685267</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>한국생산기술연구원</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>(재공고)로컬 LLM 구동용 AI 컴퓨팅 워크스테이션</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685267&amp;bidseq=000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>202607821</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>한국도로공사도로교통연구원</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>[국제입찰]비탈면 유지관리 특화 대화형 AI-Agent 시스템 개발</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=202607821&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>R26BK01671577</t>
+          <t>R26BK01667120</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>대구대학교</t>
+          <t>재단법인 경북자동차임베디드연구원</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>[대학혁신] 2026학년도 대구대학교 AI학사 챗봇 개인화 연동 고도화 사업</t>
+          <t>재직자 Skill-Up 훈련 교육용 AI 머신 운용관리 용역</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -1182,135 +1182,240 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>R26BK01685267</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(재공고)로컬 LLM 구동용 AI 컴퓨팅 워크스테이션</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685267&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>202607821</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>한국도로공사도로교통연구원</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>[국제입찰]비탈면 유지관리 특화 대화형 AI-Agent 시스템 개발</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=202607821&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01671577</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>대구대학교</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>[대학혁신] 2026학년도 대구대학교 AI학사 챗봇 개인화 연동 고도화 사업</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>R26BK01674009</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>인공지능산업융합사업단</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>AI 특화 공동훈련센터 산업 범용 AI 직무·훈련 표준모델 개발 용역</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>[AICA-26-1074] 공고문.hwp
 [AICA-26-1074] 공고문.pdf
 [AICA-26-1074] 제안요청서.hwp</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01674009&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>R26BK01676106</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>경희대학교산학협력단</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>[제2026-국제산학18호] CPU, GPU 구입</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>R26BK01677381</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>광운대학교 산학협력단</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>AI서버(NVIDIA DGX Spark)</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>R26BK01467013</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>수원과학대학교 산학협력단</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>[RISE]수원과학대학교 AI 영상면접 제작실 인테리어 공사</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>시방서(수원과학대 AI 영상면접 제작실 인테리어 공사).hwp
 간이 공내역서 - 입찰용.xlsx
@@ -1318,138 +1423,173 @@
 2025-02호 입찰유의서 및 입찰관련 서식 현황 수원과학대학교 AI 영상면접 제작실 인테리어 공사.pdf</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01467013&amp;bidseq=000</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01673277</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>선문대학교</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>선문대학교 AI 에듀테크 통합 서비스 사용</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01673925</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>한국산업기술기획평가원</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>통합 RCMS AI 공통 인프라 기반 GPU 서버 구매</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01685538</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>(재)광주테크노파크</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>광주 AI의료 상용화지원센터 통신 공사</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685538&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>R26BK01673277</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>선문대학교</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>선문대학교 AI 에듀테크 통합 서비스 사용</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026MHD005833409</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>방위사업청(운영지원과)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>국방 피지컬 AI의 자율성 등 활용방안 연구용역</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=2026MHD005833409&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01673925</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>통합 RCMS AI 공통 인프라 기반 GPU 서버 구매</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01685538</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>(재)광주테크노파크</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>광주 AI의료 상용화지원센터 통신 공사</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685538&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>R26BK01684577</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>한국화학연구원</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>AI 트레이닝 서버 구매</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>입찰공고문.pdf
 입찰공고문.hwp
@@ -1458,175 +1598,39 @@
 규격비교표.hwp</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01684577&amp;bidseq=000</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01651657</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>한국생명공학연구원</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>우선순위 감염병 치료제 라이브러리 구축용 AI 기반 구조기반 가상탐색·MD 통합분석</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>B5202602896</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>한국수자원공사 금강경영처</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>금강유역 스마트(AI)정수장 확대구축 보완 감리용역</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=B5202602896&amp;bidseq=000</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>R26BK01674285</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>재단법인 경상북도경제진흥원</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2026 상인 ·소상공인 AI 코칭 지원 사업 운영 용역</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>A042600176</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>안동빛드림본부</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>안동복합 2호기 AI기반 지능형 CCTV 2차 구매</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>G082600390</t>
+          <t>R26BK01651657</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>기획관리본부 조달협력처</t>
+          <t>한국생명공학연구원</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>AI 인프라 고도화(추론서버 구매)</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>1</v>
+          <t>우선순위 감염병 치료제 라이브러리 구축용 AI 기반 구조기반 가상탐색·MD 통합분석</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -1638,57 +1642,59 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R26BK01676166</t>
+          <t>R26BK01687189</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>동국대학교 디지털혁신팀</t>
+          <t>재단법인 대전창조경제혁신센터</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>동국대학교 AI지원 데이터 플랫폼 구축(LLM서버 납품)</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
+          <t>2026년 초기창업패키지(딥테크 특화형) ABR(AI·Bigdata·Robotics) 글로벌 스케일업 브릿지 위탁운영</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1. 재공고문.hwp
+1. 재공고문.pdf
+2. 제안요청서.hwp</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01676166&amp;bidseq=000</t>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01687189&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R26BK01675863</t>
+          <t>B5202602896</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>대구한의대학교</t>
+          <t>한국수자원공사 금강경영처</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>(대학혁신)AI시대 대응 핵심역량 진단⦁인증체계 재구조화 컨설팅 용역(재공고)</t>
+          <t>금강유역 스마트(AI)정수장 확대구축 보완 감리용역</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -1701,29 +1707,29 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/</t>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=B5202602896&amp;bidseq=000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R26BK01675859</t>
+          <t>R26BK01674285</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>(주)비아이매트릭스</t>
+          <t>재단법인 경상북도경제진흥원</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>AI 기반 건축 인허가 법령 검증 및 사전진단 체계 구축 연구(1차년도)</t>
+          <t>2026 상인 ·소상공인 AI 코칭 지원 사업 운영 용역</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -1743,100 +1749,306 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>A042600176</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>안동빛드림본부</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>안동복합 2호기 AI기반 지능형 CCTV 2차 구매</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>G082600390</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>기획관리본부 조달협력처</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>AI 인프라 고도화(추론서버 구매)</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01676166</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>동국대학교 디지털혁신팀</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>동국대학교 AI지원 데이터 플랫폼 구축(LLM서버 납품)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01676166&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01675863</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>대구한의대학교</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(대학혁신)AI시대 대응 핵심역량 진단⦁인증체계 재구조화 컨설팅 용역(재공고)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01686488</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>한국승강기안전공단</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>공단 AI시스템 구축 및 AI 민원 상담사 고도화 사업</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01686488&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01675859</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>(주)비아이매트릭스</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>AI 기반 건축 인허가 법령 검증 및 사전진단 체계 구축 연구(1차년도)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t>R26BK01682451</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>메타빌드주식회사</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>지역특화 복지안내 AI 인프라구축</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E46" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>(물품규격서) 지역특화 복지안내 AI 인프라 구축.pdf
 (제안요청서) 지역특화 복지안내 AI 인프라 구축.pdf
 (공고문) 지역특화 복지안내 AI 인프라 구축.pdf</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01682451&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>R26BK01680386</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>AI 기반 전공 탐색 및 학업설계 통합 플랫폼(1단계) 구축</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01680386&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>R26BK01674648</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>학교법인한국폴리텍 한국폴리텍대학신기술교육원</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍대학 신기술교육원 피지컬AI리빙센터 구축 공사(건축)</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>공고문_피지컬AI리빙센터 구축 공사(건축).hwp
 공고문_피지컬AI리빙센터 구축 공사(건축).pdf
@@ -1845,72 +2057,72 @@
 도면.PDF</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01674648&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>R26BK01679048</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>한국과학기술정보연구원</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>GVC 이슈 사전감지 모델 실증을 위한 모듈 및 AI 에이전트 개발</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>R26BK01680184</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>대구경북과학기술원</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>고성능 HPC 클러스터 AI 계산 시스템 구매(재공고)</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1. 공고문(DGIST 제2026-114-1호).hwp
 1. 공고문(DGIST 제2026-114-1호).pdf
@@ -1919,142 +2131,177 @@
 4. 퇴직자(재직자) 영입현황 확인서 및 수의계약 체결 제한 여부 확인서(양식).hwp</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01680184&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01682325</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>주식회사 나르마</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>AI 학습용 고사양 GPU 서버</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01682325&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>R26BK01684824</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>서울특별시 서울시립대학교</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>실험실습기자재 「AI연산용카드」구매_전자전기컴퓨터공학부</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01684824&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>R26BK01682150</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍I대학성남캠퍼스</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍대학 성남캠퍼스 피지컬AI센터 구축공사(전기)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01682150&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>R26BK01614759</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>한국지질자원연구원</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>KIGAM IP품질 강화 지원(AI 활용) 용역</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>R26BK01674924</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>학교법인한국폴리텍 한국폴리텍대학신기술교육원</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>한국폴리텍대학 신기술교육원 피지컬AI리빙센터 구축 공사(전기)</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>공고문_피지컬AI리빙센터 구축 공사(전기).hwp
 공고문_피지컬AI리빙센터 구축 공사(전기).pdf
@@ -2062,107 +2309,142 @@
 시방서(전기).pdf</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01674924&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>R26BK01679020</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>한국관광공사</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>AI 기반 주차정보 분석 및 데이터 연계 사업</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E56" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>R26BK01675691</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>경상북도교육청 포항제철공업고등학교</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>NCS기반 실습기자재(AI비전 로봇실습장비) 구매</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01686077</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>영암군농협쌀조합공동사업법인</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>2025년 고품질쌀유통활성화사업 가공시설 현대화 기계설비공사 (AI미곡종합품질관리기 물품구매 및 납품)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01686077&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>2602565</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>한국토지주택공사</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>(정정) 2026 스마트건설·안전·AI EXPO 전시부스 기획·설치·운영 용역</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>1 (정정) 입찰공고문 (2026 스마트건설·안전·AI EXPO 전시부스 기획·설치·운영 용역).hwp
 2 (정정) 요약안내.hwpx
@@ -2170,247 +2452,247 @@
 4 과업내용서 (2026 스마트건설·안전·AI EXPO 전시부스 기획·설치·운영 용역).hwpx</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>https://ebid.lh.or.kr/ebid.et.tp.cmd.BidsrvcsDetailListCmd.dev?bidNum=2602565&amp;bidDegree=01</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>R26BK01678097</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>충청남도교육청 충청남도금산교육지원청</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>2026 AI 역량강화 프로그램 위탁 용역</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E60" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>R26BK01675476</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>서울특별시 서울시립대학교</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>2026학년도 AI상담 프로그램 운영 용역</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>R26BK01678508</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>재단법인강원정보문화산업진흥원</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>2026년 AI융합경진대회사업 바이브코딩 앱 제작 교육 및 챌린지 용역</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E62" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>R26BK01674930</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>충남테크노파크</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>온디바이스AI 서비스 실증·확산 마스터플랜 수립 용역</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>3-1. 제안요청서.hwp</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>R26BK01677378</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>전북대학교병원</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>전북대학교병원 권역책임 의료기관 AI기반 진료시스템 지원사업(흉부질환 진단보조 소프트웨어)</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>R26BK01673933</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>국방과학연구소</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>AI 기반 스마트 TDL 네트워크 실험환경 구축</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>R26BK01667732</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>가천대학교</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>AI타워ㆍ지하주차장 신축공사 폐기물처리용역</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E66" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>(붙임1)입찰공고문.pdf
 (붙임2)양식.hwp
@@ -2419,107 +2701,142 @@
 (붙임5)현장설명장소 건물 주차 엘리베이터 안내.hwp</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01667732&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>R26BK01687405</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>지식재산처</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>(정책연구) IP 서비스 산업 실태조사 및 AI 기반 IP 전문인력 양성 연구</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01687405&amp;bidseq=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>G052600407</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>기획관리본부 조달협력처</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>AI 연산 자원 및 스토리지 증설 구매</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E68" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>R26BK01685422</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>광운대학교 산학협력단</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>노트북컴퓨터(LG gram Pro AI 16 16Z90U-KS5EK 1TB, 32GB)</t>
         </is>
       </c>
-      <c r="E60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="E69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685422&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>R26BK01682510</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>재단법인 전주정보문화산업진흥원</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>지역AI신뢰성 허브조성 및 확산 생태계 전략수립 용역</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E70" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>용역공고문_지역AI신뢰성 허브조성 및 확산 생태계 전략수립 용역.hwp
 용역공고문_지역AI신뢰성 허브조성 및 확산 생태계 전략수립 용역.pdf
@@ -2528,217 +2845,217 @@
 긴급입찰사유서_지역AI신뢰성 허브조성 및 확산 생태계 전략수립 용역.hwp</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01682510&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>R26BK01676210</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>한국방송공</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>(재공고) KBS 생명대기획 &lt;죽음의 비즈니스&gt; AI 활용 VFX 영상 제작</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E71" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>조달청고시제2026-39호(2026.7.13)_신구조문대비표.hwpx</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>R26BK01673363</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>한국가스안전공사</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>AI파트너시스템 기초 인프라 구축을 위한 보일러 성능 시험장비 구매</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr/</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>R26BK01685246</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>(재)광주테크노파크</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>광주 AI의료 상용화지원센터 전기공사</t>
         </is>
       </c>
-      <c r="E64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685246&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>R26BK01685445</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>광주과학기술원</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>고용량 AI 인프라 구축을 위한 고밀도 컴퓨팅 서버 실장 모듈</t>
         </is>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01685445&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>R26BK01684748</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>법제처</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>생성형 AI 법령검색 구축 감리용역</t>
         </is>
       </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="E75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=R26BK01684748&amp;bidseq=000</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>202607902</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>한국도로공사 본사</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>[긴급]AI-Ready 교통데이터 검증 및 관리체계 연구용역</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>https://www.g2b.go.kr:8081/ep/invitation/publish/bidInfoDtl.do?bidno=202607902&amp;bidseq=000</t>
         </is>
